--- a/public/building02.xlsx
+++ b/public/building02.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="17">
   <si>
     <t>Flr</t>
   </si>
   <si>
-    <t>Flat No.</t>
+    <t>FlatNo</t>
   </si>
   <si>
     <t>Type</t>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>Sold</t>
+  </si>
+  <si>
+    <t>height</t>
   </si>
   <si>
     <t>1st</t>
@@ -61,6 +64,9 @@
   </si>
   <si>
     <t>3BHK</t>
+  </si>
+  <si>
+    <t>2nd</t>
   </si>
 </sst>
 </file>
@@ -98,12 +104,27 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -319,14 +340,22 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="3.25"/>
+    <col customWidth="1" min="2" max="2" width="5.88"/>
+    <col customWidth="1" min="3" max="3" width="5.38"/>
+    <col customWidth="1" min="4" max="4" width="7.63"/>
+    <col customWidth="1" min="5" max="5" width="6.0"/>
+    <col customWidth="1" min="6" max="6" width="6.5"/>
+    <col customWidth="1" min="7" max="7" width="10.0"/>
+    <col customWidth="1" min="8" max="8" width="4.38"/>
+    <col customWidth="1" min="9" max="9" width="5.5"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -344,174 +373,403 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1">
+      <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="5">
         <v>101.0</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1">
+      <c r="D2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="5">
         <v>367.0</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="5">
         <v>53.0</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="5">
         <v>429.0</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>11</v>
+      <c r="H2" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5">
         <v>102.0</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="C3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5">
         <v>242.0</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="5">
         <v>53.0</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="5">
         <v>290.0</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>13</v>
+      <c r="H3" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="A4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="5">
         <v>103.0</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5">
         <v>432.0</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="5">
         <v>74.0</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="5">
         <v>632.0</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>13</v>
+      <c r="H4" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1">
+      <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="5">
         <v>104.0</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="5">
+        <v>334.0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>80.0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>124.0</v>
+      </c>
+      <c r="H5" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1">
-        <v>334.0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>80.0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>124.0</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="A6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="5">
         <v>105.0</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="1">
+      <c r="D6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="5">
         <v>367.0</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="5">
         <v>26.0</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="5">
         <v>242.0</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>13</v>
+      <c r="H6" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="A7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="7">
+        <v>201.0</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5">
+        <v>368.0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>27.0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>243.0</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="A8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="7">
+        <v>202.0</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5">
+        <v>369.0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>28.0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>244.0</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="A9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="7">
+        <v>203.0</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="5">
+        <v>370.0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>29.0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>245.0</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1"/>
-    <row r="11" ht="15.75" customHeight="1"/>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="7">
+        <v>204.0</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="5">
+        <v>371.0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>30.0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>246.0</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="7">
+        <v>205.0</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="5">
+        <v>372.0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>31.0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>247.0</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="7">
+        <v>206.0</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="5">
+        <v>373.0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>32.0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>248.0</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="7">
+        <v>207.0</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="5">
+        <v>374.0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>33.0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>249.0</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="7">
+        <v>208.0</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="5">
+        <v>375.0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>34.0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>250.0</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="7">
+        <v>209.0</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="5">
+        <v>376.0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>35.0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>251.0</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="7">
+        <v>210.0</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="5">
+        <v>377.0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>36.0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>252.0</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>

--- a/public/building02.xlsx
+++ b/public/building02.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="15">
   <si>
     <t>Flr</t>
   </si>
@@ -45,9 +45,6 @@
     <t>height</t>
   </si>
   <si>
-    <t>1st</t>
-  </si>
-  <si>
     <t>1BHK</t>
   </si>
   <si>
@@ -65,18 +62,26 @@
   <si>
     <t>3BHK</t>
   </si>
-  <si>
-    <t>2nd</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -104,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -120,11 +125,12 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -340,15 +346,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="3.25"/>
-    <col customWidth="1" min="2" max="2" width="5.88"/>
+    <col customWidth="1" min="1" max="1" width="3.13"/>
+    <col customWidth="1" min="2" max="2" width="6.13"/>
     <col customWidth="1" min="3" max="3" width="5.38"/>
     <col customWidth="1" min="4" max="4" width="7.63"/>
-    <col customWidth="1" min="5" max="5" width="6.0"/>
-    <col customWidth="1" min="6" max="6" width="6.5"/>
-    <col customWidth="1" min="7" max="7" width="10.0"/>
-    <col customWidth="1" min="8" max="8" width="4.38"/>
-    <col customWidth="1" min="9" max="9" width="5.5"/>
+    <col customWidth="1" min="5" max="5" width="6.25"/>
+    <col customWidth="1" min="6" max="6" width="6.88"/>
+    <col customWidth="1" min="7" max="7" width="10.63"/>
+    <col customWidth="1" min="8" max="8" width="4.63"/>
+    <col customWidth="1" min="9" max="9" width="6.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -379,410 +385,792 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="7">
+        <v>101.0</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5">
-        <v>101.0</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7">
+        <v>367.0</v>
+      </c>
+      <c r="F2" s="7">
+        <v>53.0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>429.0</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="5">
+      <c r="I2" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B3" s="7">
+        <v>102.0</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7">
+        <v>242.0</v>
+      </c>
+      <c r="F3" s="7">
+        <v>53.0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>290.0</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B4" s="7">
+        <v>103.0</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="7">
+        <v>432.0</v>
+      </c>
+      <c r="F4" s="7">
+        <v>74.0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>632.0</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B5" s="7">
+        <v>104.0</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="7">
+        <v>334.0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>80.0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>124.0</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B6" s="7">
+        <v>105.0</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="7">
         <v>367.0</v>
       </c>
-      <c r="F2" s="5">
-        <v>53.0</v>
-      </c>
-      <c r="G2" s="5">
-        <v>429.0</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="F6" s="7">
+        <v>26.0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>242.0</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7">
+        <v>106.0</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="7">
+        <v>368.0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>27.0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>243.0</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B8" s="7">
+        <v>107.0</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="7">
+        <v>369.0</v>
+      </c>
+      <c r="F8" s="7">
+        <v>28.0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>244.0</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B9" s="7">
+        <v>108.0</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="7">
+        <v>370.0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>29.0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>245.0</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B10" s="7">
+        <v>109.0</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="7">
+        <v>371.0</v>
+      </c>
+      <c r="F10" s="7">
+        <v>30.0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>246.0</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B11" s="7">
+        <v>110.0</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="7">
+        <v>372.0</v>
+      </c>
+      <c r="F11" s="7">
+        <v>31.0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>247.0</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B12" s="7">
+        <v>111.0</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="7">
+        <v>373.0</v>
+      </c>
+      <c r="F12" s="7">
+        <v>32.0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>248.0</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B13" s="7">
+        <v>112.0</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="7">
+        <v>374.0</v>
+      </c>
+      <c r="F13" s="7">
+        <v>33.0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>249.0</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B14" s="7">
+        <v>113.0</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="7">
+        <v>375.0</v>
+      </c>
+      <c r="F14" s="7">
+        <v>34.0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>250.0</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B15" s="6">
+        <v>201.0</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="7">
+        <v>376.0</v>
+      </c>
+      <c r="F15" s="7">
+        <v>35.0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>251.0</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B16" s="6">
+        <v>202.0</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="7">
+        <v>377.0</v>
+      </c>
+      <c r="F16" s="7">
+        <v>36.0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>252.0</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B17" s="6">
+        <v>203.0</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="D17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="7">
+        <v>432.0</v>
+      </c>
+      <c r="F17" s="7">
+        <v>74.0</v>
+      </c>
+      <c r="G17" s="7">
+        <v>632.0</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B18" s="6">
+        <v>204.0</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="7">
+        <v>334.0</v>
+      </c>
+      <c r="F18" s="7">
+        <v>80.0</v>
+      </c>
+      <c r="G18" s="7">
+        <v>124.0</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B19" s="6">
+        <v>205.0</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5">
-        <v>102.0</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="D19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="7">
+        <v>367.0</v>
+      </c>
+      <c r="F19" s="7">
+        <v>26.0</v>
+      </c>
+      <c r="G19" s="7">
         <v>242.0</v>
       </c>
-      <c r="F3" s="5">
-        <v>53.0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>290.0</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="H19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B20" s="6">
+        <v>206.0</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5">
-        <v>103.0</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="5">
-        <v>432.0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>74.0</v>
-      </c>
-      <c r="G4" s="5">
-        <v>632.0</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="D20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="7">
+        <v>368.0</v>
+      </c>
+      <c r="F20" s="7">
+        <v>27.0</v>
+      </c>
+      <c r="G20" s="7">
+        <v>243.0</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B21" s="6">
+        <v>207.0</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5">
-        <v>104.0</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="5">
-        <v>334.0</v>
-      </c>
-      <c r="F5" s="5">
-        <v>80.0</v>
-      </c>
-      <c r="G5" s="5">
-        <v>124.0</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="D21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="7">
+        <v>369.0</v>
+      </c>
+      <c r="F21" s="7">
+        <v>28.0</v>
+      </c>
+      <c r="G21" s="7">
+        <v>244.0</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B22" s="6">
+        <v>208.0</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5">
-        <v>105.0</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="5">
-        <v>367.0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>26.0</v>
-      </c>
-      <c r="G6" s="5">
-        <v>242.0</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="7">
-        <v>201.0</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="5">
-        <v>368.0</v>
-      </c>
-      <c r="F7" s="5">
-        <v>27.0</v>
-      </c>
-      <c r="G7" s="5">
-        <v>243.0</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="7">
-        <v>202.0</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="5">
-        <v>369.0</v>
-      </c>
-      <c r="F8" s="5">
-        <v>28.0</v>
-      </c>
-      <c r="G8" s="5">
-        <v>244.0</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="7">
-        <v>203.0</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="7">
         <v>370.0</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F22" s="7">
         <v>29.0</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G22" s="7">
         <v>245.0</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="7">
-        <v>204.0</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="H22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B23" s="6">
+        <v>209.0</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="7">
         <v>371.0</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F23" s="7">
         <v>30.0</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G23" s="7">
         <v>246.0</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="7">
-        <v>205.0</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="H23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B24" s="6">
+        <v>210.0</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="7">
         <v>372.0</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F24" s="7">
         <v>31.0</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G24" s="7">
         <v>247.0</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="7">
-        <v>206.0</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="H24" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B25" s="6">
+        <v>211.0</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="7">
         <v>373.0</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F25" s="7">
         <v>32.0</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G25" s="7">
         <v>248.0</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="7">
-        <v>207.0</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="H25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B26" s="6">
+        <v>212.0</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="7">
         <v>374.0</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F26" s="7">
         <v>33.0</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G26" s="7">
         <v>249.0</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="7">
-        <v>208.0</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="5">
+      <c r="H26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B27" s="6">
+        <v>213.0</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="7">
         <v>375.0</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F27" s="7">
         <v>34.0</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G27" s="7">
         <v>250.0</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="7">
-        <v>209.0</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="5">
-        <v>376.0</v>
-      </c>
-      <c r="F15" s="5">
-        <v>35.0</v>
-      </c>
-      <c r="G15" s="5">
-        <v>251.0</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="7">
-        <v>210.0</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="5">
-        <v>377.0</v>
-      </c>
-      <c r="F16" s="5">
-        <v>36.0</v>
-      </c>
-      <c r="G16" s="5">
-        <v>252.0</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
+      <c r="H27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="8">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+    </row>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
